--- a/SC0_refereestats.xlsx
+++ b/SC0_refereestats.xlsx
@@ -107,21 +107,21 @@
     <t>18</t>
   </si>
   <si>
+    <t>Nick Walsh</t>
+  </si>
+  <si>
+    <t>Don Robertson</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Don Robertson</t>
-  </si>
-  <si>
-    <t>Nick Walsh</t>
+    <t>Steven McLean</t>
   </si>
   <si>
     <t>John Beaton</t>
   </si>
   <si>
-    <t>Steven McLean</t>
-  </si>
-  <si>
     <t>Kevin Clancy</t>
   </si>
   <si>
@@ -134,22 +134,22 @@
     <t>Calum Scott</t>
   </si>
   <si>
+    <t>Chris Graham</t>
+  </si>
+  <si>
     <t>Ross Hardie</t>
   </si>
   <si>
-    <t>Chris Graham</t>
-  </si>
-  <si>
     <t>Colin Steven</t>
   </si>
   <si>
+    <t>Grant Irvine</t>
+  </si>
+  <si>
     <t>Lloyd Wilson</t>
   </si>
   <si>
     <t>Iain Snedden</t>
-  </si>
-  <si>
-    <t>Grant Irvine</t>
   </si>
   <si>
     <t>Dan McFarlane</t>
@@ -256,40 +256,40 @@
         <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D2" t="n">
-        <v>735.0</v>
+        <v>815.0</v>
       </c>
       <c r="E2" t="n">
-        <v>45.9375</v>
+        <v>47.94117647058823</v>
       </c>
       <c r="F2" t="n">
-        <v>9150.0</v>
+        <v>9500.0</v>
       </c>
       <c r="G2" t="n">
-        <v>571.875</v>
+        <v>558.8235294117648</v>
       </c>
       <c r="H2" t="n">
-        <v>6700.0</v>
+        <v>7900.0</v>
       </c>
       <c r="I2" t="n">
-        <v>418.75</v>
+        <v>464.70588235294116</v>
       </c>
       <c r="J2" t="n">
-        <v>33.0625</v>
+        <v>30.058823529411764</v>
       </c>
       <c r="K2" t="n">
-        <v>33.5</v>
+        <v>44.470588235294116</v>
       </c>
       <c r="L2" t="n">
-        <v>34.875</v>
+        <v>27.235294117647058</v>
       </c>
       <c r="M2" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.1675531914893615</v>
       </c>
     </row>
     <row r="3">
@@ -300,40 +300,40 @@
         <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D3" t="n">
-        <v>595.0</v>
+        <v>625.0</v>
       </c>
       <c r="E3" t="n">
-        <v>39.666666666666664</v>
+        <v>39.0625</v>
       </c>
       <c r="F3" t="n">
-        <v>7100.0</v>
+        <v>7300.0</v>
       </c>
       <c r="G3" t="n">
-        <v>473.3333333333333</v>
+        <v>456.25</v>
       </c>
       <c r="H3" t="n">
-        <v>6350.0</v>
+        <v>6550.0</v>
       </c>
       <c r="I3" t="n">
-        <v>423.3333333333333</v>
+        <v>409.375</v>
       </c>
       <c r="J3" t="n">
-        <v>34.4</v>
+        <v>37.5625</v>
       </c>
       <c r="K3" t="n">
-        <v>35.8</v>
+        <v>36.375</v>
       </c>
       <c r="L3" t="n">
-        <v>29.2</v>
+        <v>30.1875</v>
       </c>
       <c r="M3" t="n">
         <v>19.0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.0804195804195804</v>
+        <v>2.0491803278688523</v>
       </c>
     </row>
     <row r="4">
@@ -344,40 +344,40 @@
         <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="D4" t="n">
-        <v>710.0</v>
+        <v>735.0</v>
       </c>
       <c r="E4" t="n">
-        <v>47.333333333333336</v>
+        <v>45.9375</v>
       </c>
       <c r="F4" t="n">
-        <v>8200.0</v>
+        <v>9150.0</v>
       </c>
       <c r="G4" t="n">
-        <v>546.6666666666666</v>
+        <v>571.875</v>
       </c>
       <c r="H4" t="n">
-        <v>6950.0</v>
+        <v>6700.0</v>
       </c>
       <c r="I4" t="n">
-        <v>463.3333333333333</v>
+        <v>418.75</v>
       </c>
       <c r="J4" t="n">
-        <v>28.533333333333335</v>
+        <v>33.0625</v>
       </c>
       <c r="K4" t="n">
-        <v>42.06666666666667</v>
+        <v>33.5</v>
       </c>
       <c r="L4" t="n">
-        <v>25.333333333333332</v>
+        <v>34.875</v>
       </c>
       <c r="M4" t="n">
         <v>21.0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.225705329153605</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -388,40 +388,40 @@
         <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D5" t="n">
-        <v>665.0</v>
+        <v>450.0</v>
       </c>
       <c r="E5" t="n">
-        <v>51.15384615384615</v>
+        <v>32.142857142857146</v>
       </c>
       <c r="F5" t="n">
-        <v>9250.0</v>
+        <v>3200.0</v>
       </c>
       <c r="G5" t="n">
-        <v>711.5384615384615</v>
+        <v>228.57142857142858</v>
       </c>
       <c r="H5" t="n">
-        <v>8650.0</v>
+        <v>2500.0</v>
       </c>
       <c r="I5" t="n">
-        <v>665.3846153846154</v>
+        <v>178.57142857142858</v>
       </c>
       <c r="J5" t="n">
-        <v>49.61538461538461</v>
+        <v>44.642857142857146</v>
       </c>
       <c r="K5" t="n">
-        <v>36.76923076923077</v>
+        <v>42.285714285714285</v>
       </c>
       <c r="L5" t="n">
-        <v>31.46153846153846</v>
+        <v>33.07142857142857</v>
       </c>
       <c r="M5" t="n">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.261904761904762</v>
+        <v>1.4657980456026058</v>
       </c>
     </row>
     <row r="6">
@@ -432,40 +432,40 @@
         <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="D6" t="n">
-        <v>400.0</v>
+        <v>685.0</v>
       </c>
       <c r="E6" t="n">
-        <v>33.333333333333336</v>
+        <v>48.92857142857143</v>
       </c>
       <c r="F6" t="n">
-        <v>3200.0</v>
+        <v>9350.0</v>
       </c>
       <c r="G6" t="n">
-        <v>266.6666666666667</v>
+        <v>667.8571428571429</v>
       </c>
       <c r="H6" t="n">
-        <v>2300.0</v>
+        <v>8750.0</v>
       </c>
       <c r="I6" t="n">
-        <v>191.66666666666666</v>
+        <v>625.0</v>
       </c>
       <c r="J6" t="n">
-        <v>47.916666666666664</v>
+        <v>50.214285714285715</v>
       </c>
       <c r="K6" t="n">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="L6" t="n">
-        <v>31.583333333333332</v>
+        <v>32.57142857142857</v>
       </c>
       <c r="M6" t="n">
         <v>22.0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5151515151515151</v>
+        <v>2.202572347266881</v>
       </c>
     </row>
     <row r="7">
@@ -476,40 +476,40 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D7" t="n">
-        <v>445.0</v>
+        <v>465.0</v>
       </c>
       <c r="E7" t="n">
-        <v>40.45454545454545</v>
+        <v>38.75</v>
       </c>
       <c r="F7" t="n">
         <v>4500.0</v>
       </c>
       <c r="G7" t="n">
-        <v>409.09090909090907</v>
+        <v>375.0</v>
       </c>
       <c r="H7" t="n">
-        <v>3000.0</v>
+        <v>3100.0</v>
       </c>
       <c r="I7" t="n">
-        <v>272.72727272727275</v>
+        <v>258.3333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>39.0</v>
+        <v>38.25</v>
       </c>
       <c r="K7" t="n">
-        <v>50.0</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="L7" t="n">
-        <v>33.54545454545455</v>
+        <v>33.25</v>
       </c>
       <c r="M7" t="n">
         <v>21.0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9017094017094016</v>
+        <v>1.8093385214007782</v>
       </c>
     </row>
     <row r="8">
@@ -520,40 +520,40 @@
         <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D8" t="n">
-        <v>510.0</v>
+        <v>540.0</v>
       </c>
       <c r="E8" t="n">
-        <v>46.36363636363637</v>
+        <v>45.0</v>
       </c>
       <c r="F8" t="n">
         <v>6000.0</v>
       </c>
       <c r="G8" t="n">
-        <v>545.4545454545455</v>
+        <v>500.0</v>
       </c>
       <c r="H8" t="n">
         <v>4000.0</v>
       </c>
       <c r="I8" t="n">
-        <v>363.6363636363636</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>34.72727272727273</v>
+        <v>37.416666666666664</v>
       </c>
       <c r="K8" t="n">
-        <v>38.81818181818182</v>
+        <v>35.583333333333336</v>
       </c>
       <c r="L8" t="n">
-        <v>34.27272727272727</v>
+        <v>37.0</v>
       </c>
       <c r="M8" t="n">
         <v>17.0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6842105263157894</v>
+        <v>2.6470588235294117</v>
       </c>
     </row>
     <row r="9">
@@ -564,40 +564,40 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D9" t="n">
-        <v>455.0</v>
+        <v>465.0</v>
       </c>
       <c r="E9" t="n">
-        <v>41.36363636363637</v>
+        <v>38.75</v>
       </c>
       <c r="F9" t="n">
         <v>4400.0</v>
       </c>
       <c r="G9" t="n">
-        <v>400.0</v>
+        <v>366.6666666666667</v>
       </c>
       <c r="H9" t="n">
         <v>3350.0</v>
       </c>
       <c r="I9" t="n">
-        <v>304.54545454545456</v>
+        <v>279.1666666666667</v>
       </c>
       <c r="J9" t="n">
-        <v>50.81818181818182</v>
+        <v>53.75</v>
       </c>
       <c r="K9" t="n">
-        <v>41.45454545454545</v>
+        <v>38.0</v>
       </c>
       <c r="L9" t="n">
-        <v>32.09090909090909</v>
+        <v>36.583333333333336</v>
       </c>
       <c r="M9" t="n">
         <v>21.0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.887966804979253</v>
+        <v>1.7953667953667953</v>
       </c>
     </row>
     <row r="10">
@@ -608,40 +608,40 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D10" t="n">
-        <v>300.0</v>
+        <v>320.0</v>
       </c>
       <c r="E10" t="n">
-        <v>33.333333333333336</v>
+        <v>32.0</v>
       </c>
       <c r="F10" t="n">
         <v>1600.0</v>
       </c>
       <c r="G10" t="n">
-        <v>177.77777777777777</v>
+        <v>160.0</v>
       </c>
       <c r="H10" t="n">
-        <v>1400.0</v>
+        <v>1500.0</v>
       </c>
       <c r="I10" t="n">
-        <v>155.55555555555554</v>
+        <v>150.0</v>
       </c>
       <c r="J10" t="n">
-        <v>13.333333333333334</v>
+        <v>12.0</v>
       </c>
       <c r="K10" t="n">
-        <v>49.55555555555556</v>
+        <v>46.7</v>
       </c>
       <c r="L10" t="n">
-        <v>34.888888888888886</v>
+        <v>33.5</v>
       </c>
       <c r="M10" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7341040462427746</v>
+        <v>1.7204301075268817</v>
       </c>
     </row>
     <row r="11">
@@ -655,37 +655,37 @@
         <v>9.0</v>
       </c>
       <c r="D11" t="n">
-        <v>345.0</v>
+        <v>430.0</v>
       </c>
       <c r="E11" t="n">
-        <v>38.333333333333336</v>
+        <v>47.77777777777778</v>
       </c>
       <c r="F11" t="n">
-        <v>4900.0</v>
+        <v>6400.0</v>
       </c>
       <c r="G11" t="n">
-        <v>544.4444444444445</v>
+        <v>711.1111111111111</v>
       </c>
       <c r="H11" t="n">
-        <v>3900.0</v>
+        <v>5250.0</v>
       </c>
       <c r="I11" t="n">
-        <v>433.3333333333333</v>
+        <v>583.3333333333334</v>
       </c>
       <c r="J11" t="n">
-        <v>30.666666666666668</v>
+        <v>42.333333333333336</v>
       </c>
       <c r="K11" t="n">
-        <v>19.333333333333332</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="L11" t="n">
-        <v>24.444444444444443</v>
+        <v>32.22222222222222</v>
       </c>
       <c r="M11" t="n">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8852459016393444</v>
+        <v>1.699604743083004</v>
       </c>
     </row>
     <row r="12">
@@ -696,40 +696,40 @@
         <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D12" t="n">
-        <v>430.0</v>
+        <v>345.0</v>
       </c>
       <c r="E12" t="n">
-        <v>53.75</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="F12" t="n">
-        <v>6400.0</v>
+        <v>4900.0</v>
       </c>
       <c r="G12" t="n">
-        <v>800.0</v>
+        <v>544.4444444444445</v>
       </c>
       <c r="H12" t="n">
-        <v>5250.0</v>
+        <v>3900.0</v>
       </c>
       <c r="I12" t="n">
-        <v>656.25</v>
+        <v>433.3333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>47.625</v>
+        <v>30.666666666666668</v>
       </c>
       <c r="K12" t="n">
-        <v>41.25</v>
+        <v>19.333333333333332</v>
       </c>
       <c r="L12" t="n">
-        <v>36.25</v>
+        <v>24.444444444444443</v>
       </c>
       <c r="M12" t="n">
-        <v>29.0</v>
+        <v>20.0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.853448275862069</v>
+        <v>1.8852459016393444</v>
       </c>
     </row>
     <row r="13">
@@ -787,37 +787,37 @@
         <v>7.0</v>
       </c>
       <c r="D14" t="n">
-        <v>375.0</v>
+        <v>220.0</v>
       </c>
       <c r="E14" t="n">
-        <v>53.57142857142857</v>
+        <v>31.428571428571427</v>
       </c>
       <c r="F14" t="n">
-        <v>6375.0</v>
+        <v>2500.0</v>
       </c>
       <c r="G14" t="n">
-        <v>910.7142857142857</v>
+        <v>357.14285714285717</v>
       </c>
       <c r="H14" t="n">
-        <v>5200.0</v>
+        <v>800.0</v>
       </c>
       <c r="I14" t="n">
-        <v>742.8571428571429</v>
+        <v>114.28571428571429</v>
       </c>
       <c r="J14" t="n">
-        <v>50.0</v>
+        <v>36.0</v>
       </c>
       <c r="K14" t="n">
-        <v>23.142857142857142</v>
+        <v>48.857142857142854</v>
       </c>
       <c r="L14" t="n">
-        <v>27.0</v>
+        <v>42.42857142857143</v>
       </c>
       <c r="M14" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6041666666666665</v>
+        <v>1.476510067114094</v>
       </c>
     </row>
     <row r="15">
@@ -828,40 +828,40 @@
         <v>44</v>
       </c>
       <c r="C15" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D15" t="n">
-        <v>265.0</v>
+        <v>375.0</v>
       </c>
       <c r="E15" t="n">
-        <v>44.166666666666664</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="F15" t="n">
-        <v>1800.0</v>
+        <v>6375.0</v>
       </c>
       <c r="G15" t="n">
-        <v>300.0</v>
+        <v>910.7142857142857</v>
       </c>
       <c r="H15" t="n">
-        <v>1500.0</v>
+        <v>5200.0</v>
       </c>
       <c r="I15" t="n">
-        <v>250.0</v>
+        <v>742.8571428571429</v>
       </c>
       <c r="J15" t="n">
-        <v>34.833333333333336</v>
+        <v>50.0</v>
       </c>
       <c r="K15" t="n">
-        <v>23.833333333333332</v>
+        <v>23.142857142857142</v>
       </c>
       <c r="L15" t="n">
-        <v>30.833333333333332</v>
+        <v>27.0</v>
       </c>
       <c r="M15" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.0703125</v>
+        <v>2.6041666666666665</v>
       </c>
     </row>
     <row r="16">
@@ -875,37 +875,37 @@
         <v>6.0</v>
       </c>
       <c r="D16" t="n">
-        <v>135.0</v>
+        <v>265.0</v>
       </c>
       <c r="E16" t="n">
-        <v>22.5</v>
+        <v>44.166666666666664</v>
       </c>
       <c r="F16" t="n">
-        <v>850.0</v>
+        <v>1800.0</v>
       </c>
       <c r="G16" t="n">
-        <v>141.66666666666666</v>
+        <v>300.0</v>
       </c>
       <c r="H16" t="n">
-        <v>200.0</v>
+        <v>1500.0</v>
       </c>
       <c r="I16" t="n">
-        <v>33.333333333333336</v>
+        <v>250.0</v>
       </c>
       <c r="J16" t="n">
-        <v>31.833333333333332</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="K16" t="n">
-        <v>51.666666666666664</v>
+        <v>23.833333333333332</v>
       </c>
       <c r="L16" t="n">
-        <v>44.166666666666664</v>
+        <v>30.833333333333332</v>
       </c>
       <c r="M16" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0887096774193548</v>
+        <v>2.0703125</v>
       </c>
     </row>
     <row r="17">
